--- a/salidas_referencia/Boletin_AIOS TRIMESTRAL.xlsx
+++ b/salidas_referencia/Boletin_AIOS TRIMESTRAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://superfinanciera-my.sharepoint.com/personal/jemalagon_superfinanciera_gov_co/Documents/ANALITICA PENSIONES/AIOS/para transmision a jun 2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\app\plantilla-aios-macro\salidas_referencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="713" documentId="13_ncr:1_{B60D2911-20E3-44AB-BB4C-929E45F0763E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB14FC83-B048-46C1-92CB-9AD6113C2432}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EF6A36-48F8-45B6-8AE5-D65D6DB46C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="afiliados" sheetId="1" r:id="rId1"/>
@@ -1738,45 +1738,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AJ65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" style="8"/>
-    <col min="2" max="2" width="14.54296875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="17.26953125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.26953125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="14.26953125" style="8" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="20.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.26953125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" style="8" customWidth="1"/>
-    <col min="14" max="14" width="14.26953125" style="8" customWidth="1"/>
-    <col min="15" max="15" width="17.26953125" style="8" customWidth="1"/>
-    <col min="16" max="16" width="20.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.54296875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" style="8"/>
+    <col min="2" max="2" width="14.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="21.21875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="20.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.21875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="8" customWidth="1"/>
+    <col min="14" max="14" width="14.21875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="17.21875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="20.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" style="8" customWidth="1"/>
     <col min="18" max="18" width="18" style="8" customWidth="1"/>
-    <col min="19" max="19" width="10.7265625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="14.26953125" style="8" customWidth="1"/>
-    <col min="21" max="21" width="17.26953125" style="8" customWidth="1"/>
-    <col min="22" max="22" width="20.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="21.26953125" style="8" customWidth="1"/>
-    <col min="25" max="25" width="14.54296875" style="8" customWidth="1"/>
-    <col min="26" max="26" width="14.26953125" style="8" customWidth="1"/>
-    <col min="27" max="27" width="17.26953125" style="8" customWidth="1"/>
-    <col min="28" max="28" width="20.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.26953125" style="8" customWidth="1"/>
-    <col min="30" max="30" width="14.54296875" style="8" customWidth="1"/>
-    <col min="31" max="31" width="14.26953125" style="8" customWidth="1"/>
-    <col min="32" max="32" width="17.26953125" style="8" customWidth="1"/>
-    <col min="33" max="33" width="20.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.26953125" style="8" customWidth="1"/>
-    <col min="35" max="36" width="20.26953125" style="8" customWidth="1"/>
-    <col min="37" max="16384" width="9.54296875" style="8"/>
+    <col min="19" max="19" width="10.77734375" style="8" customWidth="1"/>
+    <col min="20" max="20" width="14.21875" style="8" customWidth="1"/>
+    <col min="21" max="21" width="17.21875" style="8" customWidth="1"/>
+    <col min="22" max="22" width="20.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="21.21875" style="8" customWidth="1"/>
+    <col min="25" max="25" width="14.5546875" style="8" customWidth="1"/>
+    <col min="26" max="26" width="14.21875" style="8" customWidth="1"/>
+    <col min="27" max="27" width="17.21875" style="8" customWidth="1"/>
+    <col min="28" max="28" width="20.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.21875" style="8" customWidth="1"/>
+    <col min="30" max="30" width="14.5546875" style="8" customWidth="1"/>
+    <col min="31" max="31" width="14.21875" style="8" customWidth="1"/>
+    <col min="32" max="32" width="17.21875" style="8" customWidth="1"/>
+    <col min="33" max="33" width="20.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="21.21875" style="8" customWidth="1"/>
+    <col min="35" max="36" width="20.21875" style="8" customWidth="1"/>
+    <col min="37" max="16384" width="9.5546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
@@ -1787,7 +1787,7 @@
       <c r="F1"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:36" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1797,8 +1797,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:36" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:36" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="127" t="s">
         <v>3</v>
       </c>
@@ -1889,7 +1889,7 @@
       <c r="AI6" s="125"/>
       <c r="AJ6" s="8"/>
     </row>
-    <row r="7" spans="1:36" s="10" customFormat="1" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" s="10" customFormat="1" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11" t="s">
         <v>11</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AJ7" s="8"/>
     </row>
-    <row r="8" spans="1:36" s="75" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="75" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>45170</v>
       </c>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AJ8" s="74"/>
     </row>
-    <row r="9" spans="1:36" s="75" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" s="75" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>45261</v>
       </c>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AJ9" s="74"/>
     </row>
-    <row r="10" spans="1:36" s="75" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="75" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>45352</v>
       </c>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AJ10" s="74"/>
     </row>
-    <row r="11" spans="1:36" s="75" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" s="75" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>45444</v>
       </c>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AJ11" s="74"/>
     </row>
-    <row r="12" spans="1:36" s="75" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" s="75" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>45536</v>
       </c>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AJ12" s="74"/>
     </row>
-    <row r="13" spans="1:36" s="75" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" s="75" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>45627</v>
       </c>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AJ13" s="74"/>
     </row>
-    <row r="14" spans="1:36" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>45717</v>
       </c>
@@ -2730,92 +2730,44 @@
         <v>15684</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>45809</v>
       </c>
-      <c r="B15" s="12">
-        <v>216326</v>
-      </c>
-      <c r="C15" s="12">
-        <v>113622</v>
-      </c>
-      <c r="D15" s="12">
-        <v>1036454</v>
-      </c>
-      <c r="E15" s="73">
-        <v>108633</v>
-      </c>
-      <c r="F15" s="12">
-        <v>88</v>
-      </c>
-      <c r="G15" s="12">
-        <v>198075</v>
-      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="12">
-        <v>952404</v>
-      </c>
-      <c r="N15" s="12">
-        <v>415325</v>
-      </c>
-      <c r="O15" s="12">
-        <v>9093171</v>
-      </c>
-      <c r="P15" s="12">
-        <v>458023</v>
-      </c>
-      <c r="Q15" s="12">
-        <v>12</v>
-      </c>
-      <c r="R15" s="12">
-        <v>892501</v>
-      </c>
-      <c r="S15" s="12">
-        <v>518324</v>
-      </c>
-      <c r="T15" s="12">
-        <v>230662</v>
-      </c>
-      <c r="U15" s="12">
-        <v>4119738</v>
-      </c>
-      <c r="V15" s="12">
-        <v>238918</v>
-      </c>
-      <c r="W15" s="12">
-        <v>434</v>
-      </c>
-      <c r="X15" s="12">
-        <v>506092</v>
-      </c>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
       <c r="AA15" s="16"/>
       <c r="AB15" s="16"/>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="12">
-        <v>18692</v>
-      </c>
-      <c r="AE15" s="14">
-        <v>5806</v>
-      </c>
-      <c r="AF15" s="14">
-        <v>82187</v>
-      </c>
-      <c r="AG15" s="13">
-        <v>5284</v>
-      </c>
-      <c r="AH15" s="13">
-        <v>65</v>
-      </c>
-      <c r="AI15" s="16">
-        <v>15727</v>
-      </c>
+      <c r="AD15" s="12"/>
+      <c r="AE15" s="14"/>
+      <c r="AF15" s="14"/>
+      <c r="AG15" s="13"/>
+      <c r="AH15" s="13"/>
+      <c r="AI15" s="16"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16" s="15"/>
@@ -3069,7 +3021,7 @@
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
     </row>
-    <row r="24" spans="1:35" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -4462,23 +4414,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="8"/>
-    <col min="2" max="3" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" style="8" customWidth="1"/>
-    <col min="9" max="16384" width="11.453125" style="8"/>
+    <col min="1" max="1" width="11.44140625" style="8"/>
+    <col min="2" max="3" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="128"/>
     </row>
-    <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>20</v>
       </c>
@@ -4491,7 +4443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -4500,7 +4452,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="130" t="s">
         <v>3</v>
       </c>
@@ -4513,7 +4465,7 @@
       <c r="F5" s="132"/>
       <c r="G5" s="132"/>
     </row>
-    <row r="6" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="131"/>
       <c r="B6" s="21" t="s">
         <v>5</v>
@@ -4534,7 +4486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45170</v>
       </c>
@@ -4557,7 +4509,7 @@
         <v>83461</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45261</v>
       </c>
@@ -4580,7 +4532,7 @@
         <v>84228</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45352</v>
       </c>
@@ -4603,7 +4555,7 @@
         <v>76013</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45444</v>
       </c>
@@ -4626,7 +4578,7 @@
         <v>84087</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45536</v>
       </c>
@@ -4645,7 +4597,7 @@
         <v>79101</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45627</v>
       </c>
@@ -4664,7 +4616,7 @@
         <v>80639</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45717</v>
       </c>
@@ -4683,7 +4635,7 @@
         <v>60686</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45809</v>
       </c>
@@ -4702,7 +4654,7 @@
         <v>72819</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="112"/>
       <c r="C15" s="112"/>
@@ -4731,12 +4683,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22"/>
     </row>
-    <row r="23" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23"/>
@@ -4756,16 +4708,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Hoja4"/>
   <dimension ref="A1:AN23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.54296875" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="0" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="138" t="s">
         <v>0</v>
       </c>
@@ -4776,7 +4728,7 @@
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>23</v>
       </c>
@@ -4787,7 +4739,7 @@
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>24</v>
       </c>
@@ -4798,7 +4750,7 @@
       <c r="F3" s="25"/>
       <c r="G3" s="40"/>
     </row>
-    <row r="4" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="25"/>
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
@@ -4807,7 +4759,7 @@
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="133" t="s">
         <v>3</v>
       </c>
@@ -4853,7 +4805,7 @@
       <c r="AG5" s="136"/>
       <c r="AH5" s="137"/>
     </row>
-    <row r="6" spans="1:36" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="134"/>
       <c r="B6" s="42" t="s">
         <v>5</v>
@@ -4931,7 +4883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:36" s="76" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" s="76" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>45199</v>
       </c>
@@ -5023,7 +4975,7 @@
         <v>876.7256810960688</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="76" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" s="76" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>45291</v>
       </c>
@@ -5115,7 +5067,7 @@
         <v>1032.7569650318546</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>45382</v>
       </c>
@@ -5207,7 +5159,7 @@
         <v>1028.1096094786976</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>45473</v>
       </c>
@@ -5301,7 +5253,7 @@
       <c r="AI10" s="103"/>
       <c r="AJ10" s="103"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>45536</v>
       </c>
@@ -5395,7 +5347,7 @@
       <c r="AI11" s="103"/>
       <c r="AJ11" s="103"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>45627</v>
       </c>
@@ -5489,7 +5441,7 @@
       <c r="AI12" s="103"/>
       <c r="AJ12" s="103"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>45747</v>
       </c>
@@ -5587,7 +5539,7 @@
       <c r="AI13" s="103"/>
       <c r="AJ13" s="103"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>45838</v>
       </c>
@@ -5685,20 +5637,20 @@
       <c r="AI14" s="103"/>
       <c r="AJ14" s="103"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="I15" s="84"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B18" s="77"/>
     </row>
-    <row r="19" spans="2:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:40" x14ac:dyDescent="0.3">
       <c r="AH23" s="35"/>
       <c r="AI23" s="85"/>
       <c r="AJ23" s="88"/>
@@ -5728,15 +5680,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Hoja5"/>
   <dimension ref="A1:L65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="11.453125" customWidth="1"/>
-    <col min="9" max="9" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.453125" customWidth="1"/>
-    <col min="11" max="12" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" customWidth="1"/>
+    <col min="11" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="140" t="s">
         <v>0</v>
       </c>
@@ -5751,7 +5703,7 @@
       <c r="J1" s="50"/>
       <c r="K1" s="50"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>30</v>
       </c>
@@ -5766,7 +5718,7 @@
       <c r="J2" s="50"/>
       <c r="K2" s="50"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
         <v>31</v>
       </c>
@@ -5781,7 +5733,7 @@
       <c r="J3" s="50"/>
       <c r="K3" s="50"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="53" t="s">
         <v>32</v>
       </c>
@@ -5796,7 +5748,7 @@
       <c r="J4" s="50"/>
       <c r="K4" s="50"/>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="53"/>
       <c r="B5" s="50"/>
       <c r="C5" s="50"/>
@@ -5809,7 +5761,7 @@
       <c r="J5" s="50"/>
       <c r="K5" s="50"/>
     </row>
-    <row r="6" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="53"/>
       <c r="B6" s="50"/>
       <c r="C6" s="50"/>
@@ -5822,7 +5774,7 @@
       <c r="J6" s="50"/>
       <c r="K6" s="50"/>
     </row>
-    <row r="7" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="53"/>
       <c r="B7" s="50"/>
       <c r="C7" s="50"/>
@@ -5835,7 +5787,7 @@
       <c r="J7" s="50"/>
       <c r="K7" s="50"/>
     </row>
-    <row r="8" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="53"/>
       <c r="B8" s="50"/>
       <c r="C8" s="50"/>
@@ -5848,7 +5800,7 @@
       <c r="J8" s="50"/>
       <c r="K8" s="50"/>
     </row>
-    <row r="9" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="53"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
@@ -5861,7 +5813,7 @@
       <c r="J9" s="50"/>
       <c r="K9" s="50"/>
     </row>
-    <row r="10" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="53"/>
       <c r="B10" s="50"/>
       <c r="C10" s="50"/>
@@ -5874,8 +5826,8 @@
       <c r="J10" s="50"/>
       <c r="K10" s="50"/>
     </row>
-    <row r="11" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="142" t="s">
         <v>3</v>
       </c>
@@ -5892,7 +5844,7 @@
       <c r="J12" s="50"/>
       <c r="K12" s="50"/>
     </row>
-    <row r="13" spans="1:11" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="143"/>
       <c r="B13" s="54" t="s">
         <v>5</v>
@@ -5917,7 +5869,7 @@
       <c r="J13" s="55"/>
       <c r="K13" s="50"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="109">
         <v>45199</v>
       </c>
@@ -5940,7 +5892,7 @@
         <v>52.338686068452482</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="109">
         <v>45291</v>
       </c>
@@ -5963,7 +5915,7 @@
         <v>57.164431452432581</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="109">
         <v>45382</v>
       </c>
@@ -5986,7 +5938,7 @@
         <v>60.10144422712699</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="109">
         <v>45473</v>
       </c>
@@ -6014,7 +5966,7 @@
       <c r="K17" s="105"/>
       <c r="L17" s="105"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="110">
         <v>45536</v>
       </c>
@@ -6038,7 +5990,7 @@
       </c>
       <c r="H18" s="56"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="111">
         <v>45627</v>
       </c>
@@ -6062,7 +6014,7 @@
       </c>
       <c r="H19" s="56"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="109">
         <v>45747</v>
       </c>
@@ -6085,7 +6037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="109">
         <v>45838</v>
       </c>
@@ -6108,7 +6060,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="56"/>
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
@@ -6116,7 +6068,7 @@
       <c r="F34" s="56"/>
       <c r="G34" s="56"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="56"/>
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
@@ -6124,7 +6076,7 @@
       <c r="F35" s="56"/>
       <c r="G35" s="56"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="56"/>
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
@@ -6132,7 +6084,7 @@
       <c r="F36" s="56"/>
       <c r="G36" s="56"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="56"/>
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
@@ -6140,7 +6092,7 @@
       <c r="F37" s="56"/>
       <c r="G37" s="56"/>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="56"/>
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
@@ -6148,7 +6100,7 @@
       <c r="F38" s="56"/>
       <c r="G38" s="56"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="56"/>
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
@@ -6156,7 +6108,7 @@
       <c r="F39" s="56"/>
       <c r="G39" s="56"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="56"/>
       <c r="C40" s="56"/>
       <c r="D40" s="56"/>
@@ -6164,7 +6116,7 @@
       <c r="F40" s="56"/>
       <c r="G40" s="56"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="56"/>
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
@@ -6172,7 +6124,7 @@
       <c r="F41" s="56"/>
       <c r="G41" s="56"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="56"/>
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
@@ -6180,7 +6132,7 @@
       <c r="F42" s="56"/>
       <c r="G42" s="56"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="56"/>
       <c r="C43" s="56"/>
       <c r="D43" s="56"/>
@@ -6188,7 +6140,7 @@
       <c r="F43" s="56"/>
       <c r="G43" s="56"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="56"/>
       <c r="C44" s="56"/>
       <c r="D44" s="56"/>
@@ -6196,7 +6148,7 @@
       <c r="F44" s="56"/>
       <c r="G44" s="56"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
@@ -6204,7 +6156,7 @@
       <c r="F45" s="56"/>
       <c r="G45" s="56"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="56"/>
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
@@ -6212,7 +6164,7 @@
       <c r="F46" s="56"/>
       <c r="G46" s="56"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="56"/>
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
@@ -6220,7 +6172,7 @@
       <c r="F47" s="56"/>
       <c r="G47" s="56"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="56"/>
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
@@ -6228,7 +6180,7 @@
       <c r="F48" s="56"/>
       <c r="G48" s="56"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="56"/>
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
@@ -6236,7 +6188,7 @@
       <c r="F49" s="56"/>
       <c r="G49" s="56"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="56"/>
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
@@ -6244,7 +6196,7 @@
       <c r="F50" s="56"/>
       <c r="G50" s="56"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="56"/>
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
@@ -6252,7 +6204,7 @@
       <c r="F51" s="56"/>
       <c r="G51" s="56"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="56"/>
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
@@ -6260,7 +6212,7 @@
       <c r="F52" s="56"/>
       <c r="G52" s="56"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="56"/>
       <c r="C53" s="56"/>
       <c r="D53" s="56"/>
@@ -6268,7 +6220,7 @@
       <c r="F53" s="56"/>
       <c r="G53" s="56"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="56"/>
       <c r="C54" s="56"/>
       <c r="D54" s="56"/>
@@ -6276,7 +6228,7 @@
       <c r="F54" s="56"/>
       <c r="G54" s="56"/>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="56"/>
       <c r="C55" s="56"/>
       <c r="D55" s="56"/>
@@ -6284,7 +6236,7 @@
       <c r="F55" s="56"/>
       <c r="G55" s="56"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="56"/>
       <c r="C56" s="56"/>
       <c r="D56" s="56"/>
@@ -6292,7 +6244,7 @@
       <c r="F56" s="56"/>
       <c r="G56" s="56"/>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" s="56"/>
       <c r="C57" s="56"/>
       <c r="D57" s="56"/>
@@ -6300,7 +6252,7 @@
       <c r="F57" s="56"/>
       <c r="G57" s="56"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="56"/>
       <c r="C58" s="56"/>
       <c r="D58" s="56"/>
@@ -6308,7 +6260,7 @@
       <c r="F58" s="56"/>
       <c r="G58" s="56"/>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="56"/>
@@ -6316,7 +6268,7 @@
       <c r="F59" s="56"/>
       <c r="G59" s="56"/>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="56"/>
       <c r="C60" s="56"/>
       <c r="D60" s="56"/>
@@ -6324,7 +6276,7 @@
       <c r="F60" s="56"/>
       <c r="G60" s="56"/>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="56"/>
       <c r="C61" s="56"/>
       <c r="D61" s="56"/>
@@ -6332,7 +6284,7 @@
       <c r="F61" s="56"/>
       <c r="G61" s="56"/>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="56"/>
       <c r="C62" s="56"/>
       <c r="D62" s="56"/>
@@ -6340,7 +6292,7 @@
       <c r="F62" s="56"/>
       <c r="G62" s="56"/>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="56"/>
       <c r="C63" s="56"/>
       <c r="D63" s="56"/>
@@ -6348,7 +6300,7 @@
       <c r="F63" s="56"/>
       <c r="G63" s="56"/>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="56"/>
       <c r="C64" s="56"/>
       <c r="D64" s="56"/>
@@ -6356,7 +6308,7 @@
       <c r="F64" s="56"/>
       <c r="G64" s="56"/>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="56"/>
       <c r="C65" s="56"/>
       <c r="D65" s="56"/>
@@ -6379,12 +6331,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A1:AC46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="138" t="s">
         <v>0</v>
       </c>
@@ -6402,7 +6354,7 @@
       <c r="M1" s="25"/>
       <c r="N1" s="25"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>33</v>
       </c>
@@ -6420,7 +6372,7 @@
       <c r="M2" s="25"/>
       <c r="N2" s="25"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>34</v>
       </c>
@@ -6438,7 +6390,7 @@
       <c r="M3" s="25"/>
       <c r="N3" s="25"/>
     </row>
-    <row r="4" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="28"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -6454,7 +6406,7 @@
       <c r="M4" s="25"/>
       <c r="N4" s="25"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="133" t="s">
         <v>3</v>
       </c>
@@ -6489,7 +6441,7 @@
       <c r="AB5" s="31"/>
       <c r="AC5" s="31"/>
     </row>
-    <row r="6" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="147"/>
       <c r="B6" s="149" t="s">
         <v>5</v>
@@ -6517,7 +6469,7 @@
       <c r="M6" s="149"/>
       <c r="N6" s="32"/>
     </row>
-    <row r="7" spans="1:29" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="134"/>
       <c r="B7" s="33" t="s">
         <v>37</v>
@@ -6557,7 +6509,7 @@
       </c>
       <c r="N7" s="32"/>
     </row>
-    <row r="8" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>45170</v>
       </c>
@@ -6599,7 +6551,7 @@
       </c>
       <c r="N8" s="83"/>
     </row>
-    <row r="9" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>45261</v>
       </c>
@@ -6641,7 +6593,7 @@
       </c>
       <c r="N9" s="83"/>
     </row>
-    <row r="10" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>45352</v>
       </c>
@@ -6683,7 +6635,7 @@
       </c>
       <c r="N10" s="83"/>
     </row>
-    <row r="11" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>45444</v>
       </c>
@@ -6725,7 +6677,7 @@
       </c>
       <c r="N11" s="83"/>
     </row>
-    <row r="12" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>45536</v>
       </c>
@@ -6767,7 +6719,7 @@
       </c>
       <c r="N12" s="83"/>
     </row>
-    <row r="13" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>45627</v>
       </c>
@@ -6809,7 +6761,7 @@
       </c>
       <c r="N13" s="83"/>
     </row>
-    <row r="14" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>45717</v>
       </c>
@@ -6852,7 +6804,7 @@
       </c>
       <c r="N14" s="83"/>
     </row>
-    <row r="15" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>45809</v>
       </c>
@@ -6895,7 +6847,7 @@
       </c>
       <c r="N15" s="83"/>
     </row>
-    <row r="16" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" s="76" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
       <c r="B16" s="80"/>
       <c r="C16" s="80"/>
@@ -6911,7 +6863,7 @@
       <c r="M16" s="80"/>
       <c r="N16" s="83"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="36" t="s">
         <v>39</v>
       </c>
@@ -6928,7 +6880,7 @@
       <c r="L17" s="37"/>
       <c r="M17" s="37"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="s">
         <v>40</v>
       </c>
@@ -6945,7 +6897,7 @@
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B31" s="78"/>
       <c r="C31" s="78"/>
       <c r="D31" s="78"/>
@@ -6959,7 +6911,7 @@
       <c r="L31" s="78"/>
       <c r="M31" s="78"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B32" s="78"/>
       <c r="C32" s="78"/>
       <c r="D32" s="78"/>
@@ -6973,7 +6925,7 @@
       <c r="L32" s="78"/>
       <c r="M32" s="78"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="78"/>
       <c r="C33" s="78"/>
       <c r="D33" s="78"/>
@@ -6987,7 +6939,7 @@
       <c r="L33" s="78"/>
       <c r="M33" s="78"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="78"/>
       <c r="C34" s="78"/>
       <c r="D34" s="78"/>
@@ -7001,7 +6953,7 @@
       <c r="L34" s="78"/>
       <c r="M34" s="78"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="78"/>
       <c r="C35" s="78"/>
       <c r="D35" s="78"/>
@@ -7015,7 +6967,7 @@
       <c r="L35" s="78"/>
       <c r="M35" s="78"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="78"/>
       <c r="C36" s="78"/>
       <c r="D36" s="78"/>
@@ -7029,7 +6981,7 @@
       <c r="L36" s="78"/>
       <c r="M36" s="78"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="78"/>
       <c r="C37" s="78"/>
       <c r="D37" s="78"/>
@@ -7043,7 +6995,7 @@
       <c r="L37" s="78"/>
       <c r="M37" s="78"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -7057,7 +7009,7 @@
       <c r="L38" s="78"/>
       <c r="M38" s="78"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -7071,7 +7023,7 @@
       <c r="L39" s="78"/>
       <c r="M39" s="78"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="78"/>
       <c r="C40" s="78"/>
       <c r="D40" s="78"/>
@@ -7085,7 +7037,7 @@
       <c r="L40" s="78"/>
       <c r="M40" s="78"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="78"/>
       <c r="C41" s="78"/>
       <c r="D41" s="78"/>
@@ -7099,7 +7051,7 @@
       <c r="L41" s="78"/>
       <c r="M41" s="78"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="78"/>
       <c r="C42" s="78"/>
       <c r="D42" s="78"/>
@@ -7113,7 +7065,7 @@
       <c r="L42" s="78"/>
       <c r="M42" s="78"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="78"/>
       <c r="C43" s="78"/>
       <c r="D43" s="78"/>
@@ -7127,7 +7079,7 @@
       <c r="L43" s="78"/>
       <c r="M43" s="78"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="78"/>
       <c r="C44" s="78"/>
       <c r="D44" s="78"/>
@@ -7141,7 +7093,7 @@
       <c r="L44" s="78"/>
       <c r="M44" s="78"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="78"/>
       <c r="C45" s="78"/>
       <c r="D45" s="78"/>
@@ -7155,7 +7107,7 @@
       <c r="L45" s="78"/>
       <c r="M45" s="78"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="78"/>
       <c r="C46" s="78"/>
       <c r="D46" s="78"/>
@@ -7190,9 +7142,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja7"/>
   <dimension ref="A1:R40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="140" t="s">
         <v>0</v>
       </c>
@@ -7204,7 +7156,7 @@
       <c r="G1" s="50"/>
       <c r="H1" s="50"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>41</v>
       </c>
@@ -7225,7 +7177,7 @@
       <c r="N2" s="50"/>
       <c r="O2" s="50"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="65" t="s">
         <v>43</v>
       </c>
@@ -7246,7 +7198,7 @@
       <c r="N3" s="50"/>
       <c r="O3" s="50"/>
     </row>
-    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="66"/>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -7263,7 +7215,7 @@
       <c r="N4" s="50"/>
       <c r="O4" s="50"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="150" t="s">
         <v>3</v>
       </c>
@@ -7288,7 +7240,7 @@
       <c r="N5" s="152"/>
       <c r="O5" s="152"/>
     </row>
-    <row r="6" spans="1:18" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="151"/>
       <c r="B6" s="68" t="s">
         <v>5</v>
@@ -7329,7 +7281,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="95">
         <v>45199</v>
       </c>
@@ -7373,7 +7325,7 @@
         <v>-0.57536236001939356</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="95">
         <v>45291</v>
       </c>
@@ -7417,7 +7369,7 @@
         <v>0.75329976603373261</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="95">
         <v>45382</v>
       </c>
@@ -7461,7 +7413,7 @@
         <v>3.265469158343004</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="95">
         <v>45473</v>
       </c>
@@ -7505,7 +7457,7 @@
         <v>5.0293003918167711</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="95">
         <v>45536</v>
       </c>
@@ -7550,7 +7502,7 @@
       </c>
       <c r="P11" s="104"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="95">
         <v>45627</v>
       </c>
@@ -7595,7 +7547,7 @@
       </c>
       <c r="P12" s="113"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="95">
         <v>45747</v>
       </c>
@@ -7642,7 +7594,7 @@
       <c r="Q13" s="113"/>
       <c r="R13" s="113"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="95">
         <v>45838</v>
       </c>
@@ -7689,17 +7641,17 @@
       <c r="Q14" s="113"/>
       <c r="R14" s="113"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="P15" s="118"/>
       <c r="Q15" s="113"/>
       <c r="R15" s="113"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="P16" s="114"/>
       <c r="Q16" s="113"/>
       <c r="R16" s="113"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="79"/>
       <c r="C24" s="79"/>
       <c r="D24" s="79"/>
@@ -7708,7 +7660,7 @@
       <c r="G24" s="79"/>
       <c r="H24" s="79"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="79"/>
       <c r="C25" s="79"/>
       <c r="D25" s="79"/>
@@ -7717,7 +7669,7 @@
       <c r="G25" s="79"/>
       <c r="H25" s="79"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="79"/>
       <c r="C26" s="79"/>
       <c r="D26" s="79"/>
@@ -7726,7 +7678,7 @@
       <c r="G26" s="79"/>
       <c r="H26" s="79"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="79"/>
       <c r="C27" s="79"/>
       <c r="D27" s="79"/>
@@ -7735,7 +7687,7 @@
       <c r="G27" s="79"/>
       <c r="H27" s="79"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="79"/>
       <c r="C28" s="79"/>
       <c r="D28" s="79"/>
@@ -7744,7 +7696,7 @@
       <c r="G28" s="79"/>
       <c r="H28" s="79"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="79"/>
       <c r="C29" s="79"/>
       <c r="D29" s="79"/>
@@ -7753,7 +7705,7 @@
       <c r="G29" s="79"/>
       <c r="H29" s="79"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="79"/>
       <c r="C30" s="79"/>
       <c r="D30" s="79"/>
@@ -7762,7 +7714,7 @@
       <c r="G30" s="79"/>
       <c r="H30" s="79"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="79"/>
       <c r="C31" s="79"/>
       <c r="D31" s="79"/>
@@ -7771,7 +7723,7 @@
       <c r="G31" s="79"/>
       <c r="H31" s="79"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="79"/>
       <c r="C32" s="79"/>
       <c r="D32" s="79"/>
@@ -7780,7 +7732,7 @@
       <c r="G32" s="79"/>
       <c r="H32" s="79"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="79"/>
       <c r="C33" s="79"/>
       <c r="D33" s="79"/>
@@ -7789,7 +7741,7 @@
       <c r="G33" s="79"/>
       <c r="H33" s="79"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="79"/>
       <c r="C34" s="79"/>
       <c r="D34" s="79"/>
@@ -7798,7 +7750,7 @@
       <c r="G34" s="79"/>
       <c r="H34" s="79"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="79"/>
       <c r="C35" s="79"/>
       <c r="D35" s="79"/>
@@ -7807,7 +7759,7 @@
       <c r="G35" s="79"/>
       <c r="H35" s="79"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="79"/>
       <c r="C36" s="79"/>
       <c r="D36" s="79"/>
@@ -7823,7 +7775,7 @@
       <c r="N36" s="79"/>
       <c r="O36" s="79"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="79"/>
       <c r="C37" s="79"/>
       <c r="D37" s="79"/>
@@ -7839,7 +7791,7 @@
       <c r="N37" s="79"/>
       <c r="O37" s="79"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" s="79"/>
       <c r="C38" s="79"/>
       <c r="D38" s="79"/>
@@ -7855,7 +7807,7 @@
       <c r="N38" s="79"/>
       <c r="O38" s="79"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" s="79"/>
       <c r="C39" s="79"/>
       <c r="D39" s="79"/>
@@ -7871,7 +7823,7 @@
       <c r="N39" s="79"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" s="79"/>
       <c r="C40" s="79"/>
       <c r="D40" s="79"/>
@@ -7906,9 +7858,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="153" t="s">
         <v>0</v>
       </c>
@@ -7922,7 +7874,7 @@
       <c r="I1" s="57"/>
       <c r="J1" s="57"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -7936,7 +7888,7 @@
       <c r="I2" s="57"/>
       <c r="J2" s="57"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="59" t="s">
         <v>2</v>
       </c>
@@ -7950,7 +7902,7 @@
       <c r="I3" s="57"/>
       <c r="J3" s="57"/>
     </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="60"/>
       <c r="B4" s="61"/>
       <c r="C4" s="61"/>
@@ -7965,7 +7917,7 @@
       <c r="L4" s="62"/>
       <c r="M4" s="62"/>
     </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="155" t="s">
         <v>3</v>
       </c>
@@ -7984,7 +7936,7 @@
       <c r="L5" s="62"/>
       <c r="M5" s="62"/>
     </row>
-    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="156"/>
       <c r="B6" s="63" t="s">
         <v>5</v>
@@ -8008,7 +7960,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="94">
         <v>45199</v>
       </c>
@@ -8034,7 +7986,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="94">
         <v>45291</v>
       </c>
@@ -8060,7 +8012,7 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="94">
         <v>45382</v>
       </c>
@@ -8086,7 +8038,7 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="94">
         <v>45473</v>
       </c>
@@ -8112,7 +8064,7 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>45536</v>
       </c>
@@ -8138,7 +8090,7 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>45627</v>
       </c>
@@ -8164,7 +8116,7 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="101">
         <v>45717</v>
       </c>
@@ -8190,7 +8142,7 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="101">
         <v>45809</v>
       </c>
@@ -8216,7 +8168,7 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -8236,18 +8188,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Hoja8"/>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.453125" style="8"/>
+    <col min="1" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="160"/>
     </row>
-    <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>47</v>
       </c>
@@ -8260,12 +8212,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="161" t="s">
         <v>3</v>
       </c>
@@ -8278,7 +8230,7 @@
       <c r="F5" s="163"/>
       <c r="G5" s="164"/>
     </row>
-    <row r="6" spans="1:7" s="10" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" s="10" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="162"/>
       <c r="B6" s="70" t="s">
         <v>5</v>
@@ -8299,7 +8251,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="101">
         <v>45199</v>
       </c>
@@ -8322,7 +8274,7 @@
         <v>7171</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="101">
         <v>45291</v>
       </c>
@@ -8345,7 +8297,7 @@
         <v>7081</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="101">
         <v>45382</v>
       </c>
@@ -8368,7 +8320,7 @@
         <v>6890</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="101">
         <v>45473</v>
       </c>
@@ -8391,7 +8343,7 @@
         <v>6762</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="101">
         <v>45536</v>
       </c>
@@ -8414,7 +8366,7 @@
         <v>6867</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="101">
         <v>45627</v>
       </c>
@@ -8437,7 +8389,7 @@
         <v>6544</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="101">
         <v>45717</v>
       </c>
@@ -8460,7 +8412,7 @@
         <v>6977</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="101">
         <v>45809</v>
       </c>
@@ -8483,7 +8435,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="10" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="101"/>
       <c r="B15" s="99"/>
       <c r="C15" s="99"/>
@@ -8499,12 +8451,12 @@
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
     </row>
-    <row r="17" spans="2:7" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="2:7" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
     </row>
-    <row r="19" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
       <c r="F19"/>
